--- a/data/excel/ventas_combustibles_desest.xlsx
+++ b/data/excel/ventas_combustibles_desest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Niveles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos de la serie" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Niveles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos de la serie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +22,16 @@
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="166" formatCode="mmm-yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -426,184 +438,184 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, total del mercado, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, total del mercado, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, total del mercado, sin usinas eléctricas ni bunker internacional, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, total del mercado, sin usinas eléctricas ni bunker internacional, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grado 2 (común), total del mercado, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grado 2 (común), total del mercado, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grado 3 (ultra), total del mercado, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grado 3 (ultra), total del mercado, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, total del mercado, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, total del mercado, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Ventas de nafta grado 2 (súper), total del mercado, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ventas de nafta grado 2 (súper), total del mercado, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Ventas de nafta grado 3 (ultra), total del mercado, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ventas de nafta grado 3 (ultra), total del mercado, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, YPF, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, YPF, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Shell (Raízen), desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Shell (Raízen), desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Axion (Esso / Pan American), desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Axion (Esso / Pan American), desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Trafigura (Puma), desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Trafigura (Puma), desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Refinor, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Ventas de gasoil grados 2 y 3, Refinor, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, YPF, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, YPF, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Shell (Raízen), desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Shell (Raízen), desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Axion (Esso / Pan American), desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Axion (Esso / Pan American), desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Trafigura (Puma), desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Trafigura (Puma), desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Refinor, desestacionalizada (propia, X-13)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Ventas de naftas grados 2 y 3, Refinor, desestacionalizada (propia, X-13), var. % mensual</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B2" t="n">
@@ -672,7 +684,7 @@
       <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B3" t="n">
@@ -771,7 +783,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B4" t="n">
@@ -870,7 +882,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B5" t="n">
@@ -969,7 +981,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B6" t="n">
@@ -1068,7 +1080,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B7" t="n">
@@ -1167,7 +1179,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B8" t="n">
@@ -1266,7 +1278,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B9" t="n">
@@ -1365,7 +1377,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B10" t="n">
@@ -1464,7 +1476,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B11" t="n">
@@ -1563,7 +1575,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B12" t="n">
@@ -1662,7 +1674,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B13" t="n">
@@ -1761,7 +1773,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B14" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B15" t="n">
@@ -1959,7 +1971,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B16" t="n">
@@ -2058,7 +2070,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B17" t="n">
@@ -2157,7 +2169,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B18" t="n">
@@ -2256,7 +2268,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B19" t="n">
@@ -2355,7 +2367,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B20" t="n">
@@ -2454,7 +2466,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B21" t="n">
@@ -2553,7 +2565,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B22" t="n">
@@ -2652,7 +2664,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B23" t="n">
@@ -2751,7 +2763,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B24" t="n">
@@ -2850,7 +2862,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B25" t="n">
@@ -2949,7 +2961,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B26" t="n">
@@ -3048,7 +3060,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B27" t="n">
@@ -3147,7 +3159,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B28" t="n">
@@ -3246,7 +3258,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B29" t="n">
@@ -3345,7 +3357,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B30" t="n">
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B31" t="n">
@@ -3543,7 +3555,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B32" t="n">
@@ -3642,7 +3654,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B33" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B34" t="n">
@@ -3840,7 +3852,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B35" t="n">
@@ -3939,7 +3951,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B36" t="n">
@@ -4038,7 +4050,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B37" t="n">
@@ -4137,7 +4149,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B38" t="n">
@@ -4236,7 +4248,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B39" t="n">
@@ -4335,7 +4347,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B40" t="n">
@@ -4434,7 +4446,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B41" t="n">
@@ -4533,7 +4545,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B42" t="n">
@@ -4632,7 +4644,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B43" t="n">
@@ -4731,7 +4743,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B44" t="n">
@@ -4830,7 +4842,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B45" t="n">
@@ -4929,7 +4941,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B46" t="n">
@@ -5028,7 +5040,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B47" t="n">
@@ -5127,7 +5139,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B48" t="n">
@@ -5226,7 +5238,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B49" t="n">
@@ -5325,7 +5337,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B50" t="n">
@@ -5424,7 +5436,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B51" t="n">
@@ -5523,7 +5535,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B52" t="n">
@@ -5622,7 +5634,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B53" t="n">
@@ -5721,7 +5733,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B54" t="n">
@@ -5820,7 +5832,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B55" t="n">
@@ -5919,7 +5931,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B56" t="n">
@@ -6018,7 +6030,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B57" t="n">
@@ -6117,7 +6129,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B58" t="n">
@@ -6216,7 +6228,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B59" t="n">
@@ -6315,7 +6327,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B60" t="n">
@@ -6414,7 +6426,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B61" t="n">
@@ -6513,7 +6525,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B62" t="n">
@@ -6612,7 +6624,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B63" t="n">
@@ -6711,7 +6723,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B64" t="n">
@@ -6810,7 +6822,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B65" t="n">
@@ -6909,7 +6921,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B66" t="n">
@@ -7008,7 +7020,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B67" t="n">
@@ -7107,7 +7119,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B68" t="n">
@@ -7206,7 +7218,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B69" t="n">
@@ -7305,7 +7317,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B70" t="n">
@@ -7404,7 +7416,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B71" t="n">
@@ -7503,7 +7515,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B72" t="n">
@@ -7602,7 +7614,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B73" t="n">
@@ -7701,7 +7713,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B74" t="n">
@@ -7800,7 +7812,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B75" t="n">
@@ -7899,7 +7911,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B76" t="n">
@@ -7998,7 +8010,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B77" t="n">
@@ -8097,7 +8109,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B78" t="n">
@@ -8196,7 +8208,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B79" t="n">
@@ -8295,7 +8307,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B81" t="n">
@@ -8493,7 +8505,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B82" t="n">
@@ -8592,7 +8604,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B83" t="n">
@@ -8691,7 +8703,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B84" t="n">
@@ -8790,7 +8802,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B85" t="n">
@@ -8889,7 +8901,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B86" t="n">
@@ -8988,7 +9000,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B87" t="n">
@@ -9087,7 +9099,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B88" t="n">
@@ -9186,7 +9198,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B89" t="n">
@@ -9285,7 +9297,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B90" t="n">
@@ -9384,7 +9396,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B91" t="n">
@@ -9483,7 +9495,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B92" t="n">
@@ -9582,7 +9594,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B93" t="n">
@@ -9681,7 +9693,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B94" t="n">
@@ -9780,7 +9792,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B95" t="n">
@@ -9879,7 +9891,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B96" t="n">
@@ -9978,7 +9990,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B97" t="n">
@@ -10077,7 +10089,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B98" t="n">
@@ -10176,7 +10188,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B99" t="n">
@@ -10275,7 +10287,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B100" t="n">
@@ -10374,7 +10386,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B101" t="n">
@@ -10473,7 +10485,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B102" t="n">
@@ -10572,7 +10584,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B103" t="n">
@@ -10671,7 +10683,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B104" t="n">
@@ -10770,7 +10782,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B105" t="n">
@@ -10869,7 +10881,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B106" t="n">
@@ -10968,7 +10980,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B107" t="n">
@@ -11067,7 +11079,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B108" t="n">
@@ -11166,7 +11178,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B109" t="n">
@@ -11265,7 +11277,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B110" t="n">
@@ -11368,7 +11380,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B111" t="n">
@@ -11475,7 +11487,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B112" t="n">
@@ -11582,7 +11594,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B113" t="n">
@@ -11689,7 +11701,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B114" t="n">
@@ -11796,7 +11808,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B115" t="n">
@@ -11903,7 +11915,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B116" t="n">
@@ -12010,7 +12022,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B117" t="n">
@@ -12117,7 +12129,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B118" t="n">
@@ -12224,7 +12236,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B119" t="n">
@@ -12331,7 +12343,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B120" t="n">
@@ -12438,7 +12450,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B121" t="n">
@@ -12545,7 +12557,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B122" t="n">
@@ -12652,7 +12664,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B123" t="n">
@@ -12759,7 +12771,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B124" t="n">
@@ -12866,7 +12878,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B125" t="n">
@@ -12973,7 +12985,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B126" t="n">
@@ -13080,7 +13092,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B127" t="n">
@@ -13187,7 +13199,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B128" t="n">
@@ -13294,7 +13306,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B129" t="n">
@@ -13401,7 +13413,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B130" t="n">
@@ -13508,7 +13520,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B131" t="n">
@@ -13615,7 +13627,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B132" t="n">
@@ -13722,7 +13734,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B133" t="n">
@@ -13829,7 +13841,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B134" t="n">
@@ -13936,7 +13948,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B135" t="n">
@@ -14043,7 +14055,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B136" t="n">
@@ -14150,7 +14162,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B137" t="n">
@@ -14257,7 +14269,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B138" t="n">
@@ -14364,7 +14376,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B139" t="n">
@@ -14471,7 +14483,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B140" t="n">
@@ -14578,7 +14590,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B141" t="n">
@@ -14685,7 +14697,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B142" t="n">
@@ -14792,7 +14804,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B143" t="n">
@@ -14899,7 +14911,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B144" t="n">
@@ -15006,7 +15018,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B145" t="n">
@@ -15113,7 +15125,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B146" t="n">
@@ -15220,7 +15232,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B147" t="n">
@@ -15327,7 +15339,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B148" t="n">
@@ -15434,7 +15446,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B149" t="n">
@@ -15541,7 +15553,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B150" t="n">
@@ -15648,7 +15660,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B151" t="n">
@@ -15755,7 +15767,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B152" t="n">
@@ -15862,7 +15874,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B153" t="n">
@@ -15969,7 +15981,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B154" t="n">
@@ -16076,7 +16088,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B155" t="n">
@@ -16183,7 +16195,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B156" t="n">
@@ -16290,7 +16302,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B157" t="n">
@@ -16397,7 +16409,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B158" t="n">
@@ -16504,7 +16516,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B159" t="n">
@@ -16611,7 +16623,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B160" t="n">
@@ -16718,7 +16730,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B161" t="n">
@@ -16825,7 +16837,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B162" t="n">
@@ -16932,7 +16944,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B163" t="n">
@@ -17039,7 +17051,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B164" t="n">
@@ -17146,7 +17158,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B165" t="n">
@@ -17253,7 +17265,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B166" t="n">
@@ -17360,7 +17372,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B167" t="n">
@@ -17467,7 +17479,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B168" t="n">
@@ -17574,7 +17586,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B169" t="n">
@@ -17681,7 +17693,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B170" t="n">
@@ -17788,7 +17800,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B171" t="n">
@@ -17895,7 +17907,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B172" t="n">
@@ -18002,7 +18014,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B173" t="n">
@@ -18109,7 +18121,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B174" t="n">
@@ -18216,7 +18228,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B175" t="n">
@@ -18323,7 +18335,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B176" t="n">
@@ -18430,7 +18442,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B177" t="n">
@@ -18537,7 +18549,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B178" t="n">
@@ -18644,7 +18656,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B179" t="n">
@@ -18751,7 +18763,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B180" t="n">
@@ -18858,7 +18870,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B181" t="n">
@@ -18965,7 +18977,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B182" t="n">
@@ -19072,7 +19084,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B183" t="n">
@@ -19179,7 +19191,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B184" t="n">
@@ -19286,7 +19298,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B185" t="n">
@@ -19393,7 +19405,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B186" t="n">
@@ -19500,7 +19512,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B187" t="n">
@@ -19607,7 +19619,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B188" t="n">
@@ -19714,7 +19726,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B189" t="n">
@@ -19821,7 +19833,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B190" t="n">
@@ -19928,7 +19940,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B191" t="n">
@@ -20035,7 +20047,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B192" t="n">
@@ -20142,7 +20154,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B193" t="n">
@@ -20249,7 +20261,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B194" t="n">
@@ -20356,7 +20368,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B195" t="n">
@@ -20463,7 +20475,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B196" t="n">
@@ -20570,7 +20582,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B197" t="n">
@@ -20677,7 +20689,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B198" t="n">
@@ -20784,7 +20796,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B199" t="n">
@@ -20891,7 +20903,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B200" t="n">
@@ -20998,7 +21010,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B201" t="n">
@@ -21174,7 +21186,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21T19:46:51Z</t>
+          <t>2026-10-22T13:57:24Z</t>
         </is>
       </c>
     </row>
